--- a/rubin_sizing_model_2026.xlsx
+++ b/rubin_sizing_model_2026.xlsx
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -3259,28 +3259,28 @@
         <v>3360</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>5040</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="33">
@@ -7232,31 +7232,51 @@
           <t>DP2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>DR1</t>
+        </is>
+      </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>DR1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>DR2</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>DR3</t>
+        </is>
+      </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>DR2</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>DR4</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>DR5</t>
+        </is>
+      </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>DR3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>DR6</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>DR7</t>
+        </is>
+      </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>DR4</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>DR8</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>DR9</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -9133,31 +9153,51 @@
           <t>DP2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DR1</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DR1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>DR2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DR3</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DR2</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>DR4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DR5</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DR3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>DR6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>DR7</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>DR4</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>DR8</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DR9</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -10071,7 +10111,11 @@
       <c r="B5" t="n">
         <v>2027</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>DR1</t>
+        </is>
+      </c>
       <c r="D5" s="5">
         <f>'Purchase Plan'!D11</f>
         <v/>
@@ -10112,7 +10156,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>DR1</t>
+          <t>DR2</t>
         </is>
       </c>
       <c r="D6" s="5">
@@ -10153,7 +10197,11 @@
       <c r="B7" t="n">
         <v>2029</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>DR3</t>
+        </is>
+      </c>
       <c r="D7" s="5">
         <f>'Purchase Plan'!F11</f>
         <v/>
@@ -10194,7 +10242,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>DR2</t>
+          <t>DR4</t>
         </is>
       </c>
       <c r="D8" s="5">
@@ -10235,7 +10283,11 @@
       <c r="B9" t="n">
         <v>2031</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>DR5</t>
+        </is>
+      </c>
       <c r="D9" s="5">
         <f>'Purchase Plan'!H11</f>
         <v/>
@@ -10276,7 +10328,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>DR3</t>
+          <t>DR6</t>
         </is>
       </c>
       <c r="D10" s="5">
@@ -10317,7 +10369,11 @@
       <c r="B11" t="n">
         <v>2033</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>DR7</t>
+        </is>
+      </c>
       <c r="D11" s="5">
         <f>'Purchase Plan'!J11</f>
         <v/>
@@ -10358,7 +10414,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>DR4</t>
+          <t>DR8</t>
         </is>
       </c>
       <c r="D12" s="5">
@@ -10399,7 +10455,11 @@
       <c r="B13" t="n">
         <v>2035</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>DR9</t>
+        </is>
+      </c>
       <c r="D13" s="5">
         <f>'Purchase Plan'!L11</f>
         <v/>

--- a/rubin_sizing_model_2026.xlsx
+++ b/rubin_sizing_model_2026.xlsx
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7600</v>
+        <v>17400</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C24" s="5">
-        <f>7600+C22</f>
+        <f>17400+C22</f>
         <v/>
       </c>
       <c r="D24" s="5">
@@ -5621,13 +5621,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
         <v>512</v>
       </c>
       <c r="D3" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>11800</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="C12" s="5">
-        <f>7600+MAX(0,C14)</f>
+        <f>17400+MAX(0,C14)</f>
         <v/>
       </c>
       <c r="D12" s="5">
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="C14" s="5">
-        <f>MAX(0,C11-7600)</f>
+        <f>MAX(0,C11-17400)</f>
         <v/>
       </c>
       <c r="D14" s="5">
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>7600</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="50">
@@ -10080,7 +10080,7 @@
         <v/>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7600</v>
+        <v>17400</v>
       </c>
       <c r="F4" s="5">
         <f>MAX(0,D4-E4)</f>
